--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f091fc51318e41f/デスクトップ/コンクリート試験/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{03120626-1312-4C4B-ADE2-93346B0FB35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{773B7251-8BC9-44FB-88CD-BF63A6BB794B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3D60516-0F3B-48DC-AE52-96FA4061E6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22450" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6E3E973A-5BCC-42C0-8195-1E2328A07B64}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="138">
   <si>
     <t>id</t>
   </si>
@@ -102,12 +102,6 @@
   </si>
   <si>
     <t>夏期において練上がり温度が高くなることが予想されたので、所定のスランプおよび空気量を得るために、AE 剤の使用量を増加した。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">夏の暑さ対策
-変化: 暑いとコンクリートはすぐ乾いて硬くなり、空気も減ります。
-補正: 減った分を補うために、薬（AE剤）を多めに投入します。
-</t>
   </si>
   <si>
     <t>細骨材を粗粒率が大きいものに変更したので、同一のスランプとなるように、単位水量を変えずに細骨材率を大きくした。</t>
@@ -348,6 +342,344 @@
 ※正しくは「底面に設置されたメッシュ金網から排出される水を計量する」です。
 （4） 【誤り】土木学会規準 JSCE-F 511（高流動コンクリートの充填試験方法（案））は、高流動コンクリートの充填性を評価する試験で、異形棒鋼を柵状に配置した流動障害を通過して、任意に定めた流動距離までの到達時間および最終的に到達する流動距離を測定する。
 ※正しくは「流動障害を通過して、反対側の部屋に充填された高さを測定する」です。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t xml:space="preserve">夏の暑さ対策
+変化: 暑いとコンクリートはすぐ乾いて硬くなり、空気も減ります。
+補正: 減った分を補うために、薬（AE剤）を多めに投入します。
+</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>③環境・経年による劣化</t>
+    <rPh sb="1" eb="3">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケイネン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>レッカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>コンクリートのアルカリシリカ反応に関する次の一般的な記述のうち、適当なものはどれか。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(1) セメント中のアルカリ量、骨材の種類が同一であれば、骨材の粒度が変わっても、反応性骨材のペシマム量は変化しない。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(2) 鉄筋コンクリート柱の場合には、主(鉄)筋によって軸方向の膨張が拘束され、主(鉄)筋に直角方向のひび割れが生じやすい。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(3) 湿潤状態にあるコンクリート構造物に対して、外部からの水分の侵入を防止する目的で表面被覆を行うと、内部の水分の逸散が妨げられアルカリシリカ反応がむしろ進行することがある。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(4) 塩化カルシウムを主成分とする凍結防止剤が散布されて外来塩分の影響を受ける構造物の場合は、アルカリが供給されるためアルカリシリカ反応が促進される。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>セメント中のアルカリ量、骨材の種類が同一であれば、骨材の粒度が変わっても、反応性骨材のペシマム量は変化しない。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>鉄筋コンクリート柱の場合には、主(鉄)筋によって軸方向の膨張が拘束され、主(鉄)筋に直角方向のひび割れが生じやすい。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>湿潤状態にあるコンクリート構造物に対して、外部からの水分の侵入を防止する目的で表面被覆を行うと、内部の水分の逸散が妨げられアルカリシリカ反応がむしろ進行することがある。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>塩化カルシウムを主成分とする凍結防止剤が散布されて外来塩分の影響を受ける構造物の場合は、アルカリが供給されるためアルカリシリカ反応が促進される。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【誤り】アルカリシリカ反応（ASR）は骨材の表面で起こる反応です。そのため、骨材の粒度が変わり表面積が変化すれば、反応が最大になる「ペシマム量」も変動します。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【誤り】： 鉄筋がある方向は膨張が抑えられる（拘束される）ため、ひび割れは鉄筋に沿って「平行」な方向に発生します。「直角」ではありません。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【誤り】： ASRを促進させるのはナトリウムやカリウムといった「アルカリ金属」です。塩化カルシウムのカルシウムイオンはこれに該当しないため、反応は促進されません。促進させるのは「塩化ナトリウム」などを主成分とするものです。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>正解。記載のとおりです。外部からの水分侵入を防ぐ表面被覆が、内部水分の逸散を妨げて反応を促進させることがあります。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【誤り】(1) アルカリシリカ反応（ASR）は骨材の表面で起こる反応です。そのため、骨材の粒度が変わり表面積が変化すれば、反応が最大になる「ペシマム量」も変動します。
+【誤り】(2) ： 鉄筋がある方向は膨張が抑えられる（拘束される）ため、ひび割れは鉄筋に沿って「平行」な方向に発生します。「直角」ではありません。
+(3)：正解。記載のとおりです。外部からの水分侵入を防ぐ表面被覆が、内部水分の逸散を妨げて反応を促進させることがあります。
+【誤り】(4) ： ASRを促進させるのはナトリウムやカリウムといった「アルカリ金属」です。塩化カルシウムのカルシウムイオンはこれに該当しないため、反応は促進されません。促進させるのは「塩化ナトリウム」などを主成分とするものです。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>⑤製造・品質管理</t>
+    <rPh sb="1" eb="3">
+      <t>セイゾウ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ヒンシツカンリ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>コンクリートの計量および練混ぜに関する次の記述のうち、JIS A 5308（レディーミクストコンクリート）の規定に照らして、不適当なものはどれか。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(1) あらかじめ計量してある高性能AE減水剤と水を一緒に累加して容積で計量した。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(2) 購入者の指定を受け JIS A 5041（コンクリート用砕石粉）に適合する砕石粉を使用する際、計量値の誤差が1回計量分量に対して±2％以内となるように計量した。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(3) バッチ濃度調整方法でスラッジ水の濃度を一定に管理し、スラッジ固形分率が3.0％以下になるように、上澄水と混合して計量した。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(4) JIS A 8603-2（コンクリートミキサー第2部：練混ぜ性能試験方法）に定める試験を行い、求めた圧縮強度、空気量およびスランプの偏差率に基づいて、コンクリートの練混ぜ量および練混ぜ時間を決定した。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(1) 水はあらかじめ計量してある混和剤と一緒に累加して計量してもよいことから、適当。
+(2) コンクリート用砕石粉は混和材で、許容計量誤差は±2％。適当。
+(3) スラッジ固形分率が3.0％以下は回収水の品質基準に適合。適当。
+【誤り】(4) JIS A 8603-2は、コンクリートの練混ぜ量を公称容量の場合と公称容量の1/2の場合でのミキサの練混ぜ性能の確認で、コンクリートの練混ぜ量と練混ぜ時間の決定をするものではない。</t>
+    <rPh sb="119" eb="120">
+      <t>アヤマ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>正解。記載のとおりです。水はあらかじめ計量してある混和剤と一緒に累加して計量してもよいことから、適当。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>正解。記載のとおりです。コンクリート用砕石粉は混和材で、許容計量誤差は±2％。適当。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>正解。記載のとおりです。スラッジ固形分率が3.0％以下は回収水の品質基準に適合。適当。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【誤り】JIS A 8603-2は、コンクリートの練混ぜ量を公称容量の場合と公称容量の1/2の場合でのミキサの練混ぜ性能の確認で、コンクリートの練混ぜ量と練混ぜ時間の決定をするものではない。</t>
+    <rPh sb="1" eb="2">
+      <t>アヤマ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>⑥施工</t>
+    <rPh sb="1" eb="3">
+      <t>セコウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>あらかじめ計量してある高性能AE減水剤と水を一緒に累加して容積で計量した。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>購入者の指定を受け JIS A 5041（コンクリート用砕石粉）に適合する砕石粉を使用する際、計量値の誤差が1回計量分量に対して±2％以内となるように計量した。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>バッチ濃度調整方法でスラッジ水の濃度を一定に管理し、スラッジ固形分率が3.0％以下になるように、上澄水と混合して計量した。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>JIS A 8603-2（コンクリートミキサー第2部：練混ぜ性能試験方法）に定める試験を行い、求めた圧縮強度、空気量およびスランプの偏差率に基づいて、コンクリートの練混ぜ量および練混ぜ時間を決定した。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ポンプによるコンクリートの圧送に関する次の記述のうち、不適当なものはどれか。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(1) コンクリートポンプは、上向き垂直管、テーパ管、ベント管およびフレキシブルホースの水平換算距離と水平管の長さによって計算された圧送負荷の 1.25 倍を上回る吐出圧力を有する機種を選定する必要がある。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(2) 下向きに圧送する場合は、上向きの圧送の場合に比べ、配管内のコンクリートの自重による圧送負荷が無視できるので、閉塞する可能性は小さくなる。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(3) 吸水率が高い人工軽量骨材を低い含水状態で用いたコンクリートを圧送すると、圧力によって骨材が吸水するので、閉塞を生じやすい。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(4) コンクリートを高所に圧送する場合は、圧送を中断したときにコンクリートの自重によって逆流が生じやすいので、ポンプの吐出口に近い水平管に逆止弁を取り付けるのがよい。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(1) 機種の選定
+計算された圧送負荷に、コンクリートの品質変動や機械的損失を考慮した係数（1.25）を乗じることから適切。
+【誤り】(2) 下り配管の閉塞
+下り配管では、コンクリートの自重により落下して材料分離が生じやすく、また配管途中で負圧状態となることにより、閉塞することが懸念されるため不適当。
+(3) 人工軽量骨材の圧送
+問題文の通り「圧力による骨材の吸水」が閉塞の原因となるため適当です
+(4) 逆流防止対策
+問題文の通り「自重による逆流」を防ぐための逆止弁設置は適切です</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>コンクリートを高所に圧送する場合は、圧送を中断したときにコンクリートの自重によって逆流が生じやすいので、ポンプの吐出口に近い水平管に逆止弁を取り付けるのがよい。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>吸水率が高い人工軽量骨材を低い含水状態で用いたコンクリートを圧送すると、圧力によって骨材が吸水するので、閉塞を生じやすい。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>下向きに圧送する場合は、上向きの圧送の場合に比べ、配管内のコンクリートの自重による圧送負荷が無視できるので、閉塞する可能性は小さくなる。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>コンクリートポンプは、上向き垂直管、テーパ管、ベント管およびフレキシブルホースの水平換算距離と水平管の長さによって計算された圧送負荷の 1.25 倍を上回る吐出圧力を有する機種を選定する必要がある。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>正解。記載のとおりです。
+機種の選定。計算された圧送負荷に、コンクリートの品質変動や機械的損失を考慮した係数（1.25）を乗じることから適切。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【誤り】下り配管の閉塞
+下り配管では、コンクリートの自重により落下して材料分離が生じやすく、また配管途中で負圧状態となることにより、閉塞することが懸念されるため不適当。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>正解。記載のとおりです。問題文の通り「圧力による骨材の吸水」が閉塞の原因となるため適当です。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>正解。記載のとおりです。問題文の通り「自重による逆流」を防ぐための逆止弁設置は適切です。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>⑦特殊コンクリート</t>
+    <rPh sb="1" eb="3">
+      <t>トクシュ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>マスコンクリートの施工において、有害な温度ひび割れが発生する可能性がある構造物では、構造体に生じた( a )に対するコンクリートの( b )の比として定義されるひび割れ指数を用いて、ひび割れ発生の可能性を評価する。なお、同じひび割れ指数でも鉄筋の量を多くすると、( c )することができる。
+| | a | b | c |
+| :--- | :--- | :--- | :--- |
+| (1) | 主引張ひずみ | ひび割れ発生時ひずみ | ひび割れの幅を小さく |
+| (2) | 主引張ひずみ | ひび割れ発生時ひずみ | ひび割れの本数を少なく |
+| (3) | 主引張応力 | 引張強度 | ひび割れの本数を少なく |
+| (4) | 主引張応力 | 引張強度 | ひび割れの幅を小さく |</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(1) a：主引張ひずみ ｜ b：ひび割れ発生時ひずみ ｜ c：ひび割れの幅を小さく</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(2) a：主引張ひずみ ｜ b：ひび割れ発生時ひずみ ｜ c：ひび割れの本数を少なく</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(3) a：主引張応力 ｜ b：引張強度 ｜ c：ひび割れの本数を少なく</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(4) a：主引張応力 ｜ b：引張強度 ｜ c：ひび割れの幅を小さく</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【正解】(4)
+ひび割れ指数のルール (a, b):
+「コンクリートが耐えられる強さ（引張強度）」を「外から引っ張られる力（主引張応力）」で割って計算します。
+この数字が 1.0 を下回ると、「耐える力」よりも「壊そうとする力」が勝ちはじめるため、50％以上の確率でひび割れが発生してしまいます。
+鉄筋の本当の役割 (c):
+ひび割れをまたぐように入れる鉄筋は、ひび割れそのものをゼロにする魔法の杖ではありません。
+鉄筋の役割は、ひび割れが起きたときにそれが大きく開かないように「ギュッ」とつなぎ止めて、ひび割れの幅を細かく、小さく抑えることにあります。
+そのため、鉄筋をたくさん入れると、ひび割れの幅を小さくすることができます。</t>
+    <rPh sb="1" eb="3">
+      <t>セイカイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>⑧構造・設計・ひび割れ</t>
+    <rPh sb="1" eb="3">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>曲げモーメントが作用する鉄筋コンクリート梁の設計の考え方に関する次の記述のうち、適当なものはどれか。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(1) 断面に生じる水平方向のひずみは、曲げひび割れ発生後においても中立軸位置からの距離に比例すると考える。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(2) あばら筋（スターラップ）に囲まれたコンクリート断面は、圧縮力および引張力を負担すると考える。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(3) コンクリートのかぶり部分は、圧縮力および引張力のいずれも負担しないと考える。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(4) 主（鉄）筋の弾性係数（ヤング係数）は、鉄筋のリラクセーションの影響を考慮して、引張強度試験で得られた値を低減する。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(1) 平面保持の仮定：適当梁が曲がる際、変形前の平面は変形後も平面を保つという設計上の大前提です。このため、ひずみの大きさは中立軸からの距離に直線的に比例します。これはひび割れ発生後も成り立つものとして計算します。
+【誤り】(2)・(3) コンクリートの役割：不適当RC設計では「圧縮はコンクリート、引張は鉄筋」と役割を分けます。ひび割れ面ではコンクリートの引張力はゼロとみなしますが、圧縮側のコンクリート（かぶり部分を含む）はしっかりと力を負担します。
+【誤り】(4) 鉄筋のヤング係数：不適当鉄筋のヤング係数は強度や時間の経過（リラクセーション）によって変化しない一定の値（$2.0 \times 10^5 \text{ N/mm}^2$）として扱います。低減させる必要はありません。</t>
+    <rPh sb="111" eb="112">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="232" eb="233">
+      <t>アヤマ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>平面保持の仮定：適当梁が曲がる際、変形前の平面は変形後も平面を保つという設計上の大前提です。このため、ひずみの大きさは中立軸からの距離に直線的に比例します。これはひび割れ発生後も成り立つものとして計算します。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>断面に生じる水平方向のひずみは、曲げひび割れ発生後においても中立軸位置からの距離に比例すると考える。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>あばら筋（スターラップ）に囲まれたコンクリート断面は、圧縮力および引張力を負担すると考える。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【誤り】鉄筋のヤング係数：不適当鉄筋のヤング係数は強度や時間の経過（リラクセーション）によって変化しない一定の値（$2.0 \times 10^5 \text{ N/mm}^2$）として扱います。低減させる必要はありません。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>【誤り】コンクリートの役割：不適当RC設計では「圧縮はコンクリート、引張は鉄筋」と役割を分けます。ひび割れ面ではコンクリートの引張力はゼロとみなしますが、圧縮側のコンクリート（かぶり部分を含む）はしっかりと力を負担します。</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1329,10 +1661,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79889F30-8285-4FBE-A81D-08A1266ADDD4}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="6" width="8.6640625" style="2"/>
+    <col min="1" max="1" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="8.6640625" style="2"/>
     <col min="7" max="7" width="30.1640625" style="2" customWidth="1"/>
     <col min="8" max="16384" width="8.6640625" style="2"/>
   </cols>
@@ -1392,7 +1725,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
@@ -1485,7 +1818,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>20</v>
@@ -1508,13 +1841,13 @@
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>20</v>
@@ -1537,25 +1870,25 @@
         <v>12</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1572,13 +1905,13 @@
         <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>20</v>
@@ -1601,13 +1934,13 @@
         <v>12</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>20</v>
@@ -1630,13 +1963,13 @@
         <v>12</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>20</v>
@@ -1659,13 +1992,13 @@
         <v>12</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>20</v>
@@ -1685,28 +2018,28 @@
         <v>2017</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="K12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1720,16 +2053,16 @@
         <v>2017</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>20</v>
@@ -1749,16 +2082,16 @@
         <v>2017</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>20</v>
@@ -1778,16 +2111,16 @@
         <v>2017</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>20</v>
@@ -1807,16 +2140,16 @@
         <v>2017</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>20</v>
@@ -1836,28 +2169,28 @@
         <v>2016</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1871,16 +2204,16 @@
         <v>2016</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>20</v>
@@ -1900,16 +2233,16 @@
         <v>2016</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>20</v>
@@ -1929,16 +2262,16 @@
         <v>2016</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>20</v>
@@ -1958,26 +2291,642 @@
         <v>2016</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="H21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="2">
+        <v>20161400</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2016</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="2">
+        <v>20161401</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2016</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="2">
+        <v>20161402</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2016</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="2">
+        <v>20161403</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2016</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="2">
+        <v>20161404</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2016</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="2">
+        <v>20151200</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="2">
+        <v>20151201</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="2">
+        <v>20151202</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="2">
+        <v>20151203</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="2">
+        <v>20151204</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="2">
+        <v>20171900</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="2">
+        <v>2017</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="2">
+        <v>20171901</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="2">
+        <v>2017</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="2">
+        <v>20171902</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2017</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="2">
+        <v>20171903</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2017</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="2">
+        <v>20171904</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="2">
+        <v>2017</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="2">
+        <v>20152200</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="2">
+        <v>20182400</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2018</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="2">
+        <v>20182401</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="2">
+        <v>2018</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="2">
+        <v>20182402</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="2">
+        <v>2018</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="2">
+        <v>20182403</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="2">
+        <v>2018</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="2">
+        <v>20182404</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="2">
+        <v>2018</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f091fc51318e41f/デスクトップ/コンクリート試験/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3D60516-0F3B-48DC-AE52-96FA4061E6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D11C6CFA-8B89-42E6-8192-C9093B1C791D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22450" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6E3E973A-5BCC-42C0-8195-1E2328A07B64}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="138">
   <si>
     <t>id</t>
   </si>
@@ -2854,6 +2854,12 @@
       <c r="G39" s="2" t="s">
         <v>133</v>
       </c>
+      <c r="H39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="40" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2">
@@ -2877,6 +2883,12 @@
       <c r="G40" s="2" t="s">
         <v>137</v>
       </c>
+      <c r="H40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="41" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2">
@@ -2900,6 +2912,12 @@
       <c r="G41" s="2" t="s">
         <v>137</v>
       </c>
+      <c r="H41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="42" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2">
@@ -2922,6 +2940,12 @@
       </c>
       <c r="G42" s="2" t="s">
         <v>136</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/quiz_data.xlsx
+++ b/quiz_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f091fc51318e41f/デスクトップ/コンクリート試験/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D11C6CFA-8B89-42E6-8192-C9093B1C791D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{D11C6CFA-8B89-42E6-8192-C9093B1C791D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{273090F4-DD2E-4978-9F43-325F701DFCF3}"/>
   <bookViews>
     <workbookView xWindow="22450" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6E3E973A-5BCC-42C0-8195-1E2328A07B64}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="140">
   <si>
     <t>id</t>
   </si>
@@ -680,6 +680,14 @@
   </si>
   <si>
     <t>【誤り】コンクリートの役割：不適当RC設計では「圧縮はコンクリート、引張は鉄筋」と役割を分けます。ひび割れ面ではコンクリートの引張力はゼロとみなしますが、圧縮側のコンクリート（かぶり部分を含む）はしっかりと力を負担します。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>コンクリートのかぶり部分は、圧縮力および引張力のいずれも負担しないと考える。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>主（鉄）筋の弾性係数（ヤング係数）は、鉄筋のリラクセーションの影響を考慮して、引張強度試験で得られた値を低減する。</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -2904,7 +2912,7 @@
         <v>126</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>22</v>
@@ -2933,7 +2941,7 @@
         <v>126</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>22</v>
